--- a/data/lists.xlsx
+++ b/data/lists.xlsx
@@ -5,18 +5,18 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\win10\Dropbox\Claude Projects\Visual Studio\DailyPlan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\win10\Dropbox\Claude Projects\Visual Studio\Safety Department\DailyPlan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A616367A-1C37-4FBE-8993-0A5B6CC8B562}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF9A451B-E58E-49AA-AFDE-719ACF507A73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12360" xr2:uid="{C19F27C1-C3DB-464A-959C-6DE7D328B4BC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{C19F27C1-C3DB-464A-959C-6DE7D328B4BC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$1:$B$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$1:$C$22</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="86">
   <si>
     <t>Phone</t>
   </si>
@@ -54,9 +54,6 @@
     <t>Khaled Mohamed Mansour</t>
   </si>
   <si>
-    <t>Kariem Wakied Badawy</t>
-  </si>
-  <si>
     <t>Abd Raoof Faried Abd Raoof</t>
   </si>
   <si>
@@ -210,21 +207,12 @@
     <t>+20 10 18162219</t>
   </si>
   <si>
-    <t>Alaa Nasr Zaki</t>
-  </si>
-  <si>
-    <t>ق د ع 4952</t>
-  </si>
-  <si>
     <t>Ashraf Adel</t>
   </si>
   <si>
     <t>ع ع 7371</t>
   </si>
   <si>
-    <t>Tamer khalil</t>
-  </si>
-  <si>
     <t>ر ل ق 1857</t>
   </si>
   <si>
@@ -244,6 +232,60 @@
   </si>
   <si>
     <t>Car Plate No.</t>
+  </si>
+  <si>
+    <t>Kariem Waleed Badawy</t>
+  </si>
+  <si>
+    <t>Tamer Khalil</t>
+  </si>
+  <si>
+    <t>Sameh Abd El Fatah Ebada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Islam Ead </t>
+  </si>
+  <si>
+    <t>م د ف 4658</t>
+  </si>
+  <si>
+    <t>ق د ع   4952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alaa Nasr </t>
+  </si>
+  <si>
+    <t>Hassan Hemida</t>
+  </si>
+  <si>
+    <t>8497 ر ن ي</t>
+  </si>
+  <si>
+    <t>Elsayed Mohamed</t>
+  </si>
+  <si>
+    <t>ر ج ه 3873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ahmed Ramadan </t>
+  </si>
+  <si>
+    <t>و ه 2729</t>
+  </si>
+  <si>
+    <t>Ahmed salah</t>
+  </si>
+  <si>
+    <t>ا د ل 5826</t>
+  </si>
+  <si>
+    <t>ع ف ب 7147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reda Mohamed </t>
+  </si>
+  <si>
+    <t>Refnum</t>
   </si>
 </sst>
 </file>
@@ -287,9 +329,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -625,346 +668,500 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B80D4F4C-34F7-426E-A8C0-5AD9C9F9041F}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="25.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.77734375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.5546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="20.77734375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4" customWidth="1"/>
+    <col min="7" max="7" width="20.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="3.6640625" customWidth="1"/>
+    <col min="10" max="10" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.21875" customWidth="1"/>
+    <col min="15" max="15" width="20.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="E1" t="s">
+      <c r="J1" t="s">
         <v>23</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="K1" t="s">
         <v>24</v>
       </c>
-      <c r="I1" t="s">
+      <c r="L1" t="s">
         <v>25</v>
       </c>
-      <c r="J1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L1" t="s">
-        <v>70</v>
-      </c>
-      <c r="M1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="N1" t="s">
+        <v>85</v>
+      </c>
+      <c r="O1" t="s">
+        <v>66</v>
+      </c>
+      <c r="P1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1000140290</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="B2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2">
+        <v>1027805566</v>
+      </c>
+      <c r="G2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H2" t="s">
         <v>48</v>
       </c>
-      <c r="F2" t="s">
-        <v>49</v>
-      </c>
-      <c r="H2" t="s">
-        <v>41</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
+        <v>40</v>
+      </c>
+      <c r="K2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L2" t="s">
         <v>28</v>
       </c>
-      <c r="J2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L2" t="s">
-        <v>60</v>
-      </c>
-      <c r="M2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="N2">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>1006449785</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="O2" t="s">
+        <v>79</v>
+      </c>
+      <c r="P2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="2">
+        <v>1026785300</v>
+      </c>
+      <c r="G3" t="s">
+        <v>43</v>
+      </c>
+      <c r="H3" t="s">
         <v>44</v>
-      </c>
-      <c r="F3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I3" t="s">
-        <v>30</v>
       </c>
       <c r="J3" t="s">
         <v>31</v>
       </c>
+      <c r="K3" t="s">
+        <v>29</v>
+      </c>
       <c r="L3" t="s">
+        <v>30</v>
+      </c>
+      <c r="O3" t="s">
+        <v>59</v>
+      </c>
+      <c r="P3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="2">
+        <v>1010755944</v>
+      </c>
+      <c r="G4" t="s">
+        <v>45</v>
+      </c>
+      <c r="H4" t="s">
+        <v>46</v>
+      </c>
+      <c r="J4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K4" t="s">
+        <v>32</v>
+      </c>
+      <c r="L4" t="s">
+        <v>33</v>
+      </c>
+      <c r="N4">
+        <v>3</v>
+      </c>
+      <c r="O4" t="s">
+        <v>75</v>
+      </c>
+      <c r="P4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="2">
+        <v>1022843722</v>
+      </c>
+      <c r="G5" t="s">
+        <v>49</v>
+      </c>
+      <c r="H5" t="s">
+        <v>50</v>
+      </c>
+      <c r="J5" t="s">
+        <v>38</v>
+      </c>
+      <c r="K5" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5" t="s">
+        <v>35</v>
+      </c>
+      <c r="N5">
+        <v>8</v>
+      </c>
+      <c r="O5" t="s">
+        <v>69</v>
+      </c>
+      <c r="P5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="2">
+        <v>1000385262</v>
+      </c>
+      <c r="G6" t="s">
+        <v>54</v>
+      </c>
+      <c r="H6" t="s">
+        <v>53</v>
+      </c>
+      <c r="J6" t="s">
+        <v>39</v>
+      </c>
+      <c r="K6" t="s">
+        <v>36</v>
+      </c>
+      <c r="O6" t="s">
+        <v>64</v>
+      </c>
+      <c r="P6" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="2">
+        <v>1006449785</v>
+      </c>
+      <c r="G7" t="s">
+        <v>51</v>
+      </c>
+      <c r="H7" t="s">
+        <v>52</v>
+      </c>
+      <c r="K7" t="s">
+        <v>37</v>
+      </c>
+      <c r="N7">
+        <v>10</v>
+      </c>
+      <c r="O7" t="s">
         <v>62</v>
       </c>
-      <c r="M3" t="s">
+      <c r="P7" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="2">
+        <v>1006440573</v>
+      </c>
+      <c r="G8" t="s">
+        <v>55</v>
+      </c>
+      <c r="H8" t="s">
+        <v>56</v>
+      </c>
+      <c r="N8">
+        <v>12</v>
+      </c>
+      <c r="O8" t="s">
+        <v>81</v>
+      </c>
+      <c r="P8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C9" s="2">
+        <v>1000479653</v>
+      </c>
+      <c r="G9" t="s">
+        <v>57</v>
+      </c>
+      <c r="H9" t="s">
+        <v>58</v>
+      </c>
+      <c r="N9">
+        <v>13</v>
+      </c>
+      <c r="O9" t="s">
+        <v>77</v>
+      </c>
+      <c r="P9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="2">
+        <v>1050119377</v>
+      </c>
+      <c r="G10" t="s">
+        <v>41</v>
+      </c>
+      <c r="H10" t="s">
+        <v>42</v>
+      </c>
+      <c r="N10">
+        <v>19</v>
+      </c>
+      <c r="O10" t="s">
+        <v>84</v>
+      </c>
+      <c r="P10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="2">
+        <v>1098512220</v>
+      </c>
+      <c r="N11">
+        <v>21</v>
+      </c>
+      <c r="O11" t="s">
+        <v>74</v>
+      </c>
+      <c r="P11" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
+      <c r="C12" s="2">
         <v>1020004089</v>
       </c>
-      <c r="E4" t="s">
-        <v>46</v>
-      </c>
-      <c r="F4" t="s">
-        <v>47</v>
-      </c>
-      <c r="H4" t="s">
-        <v>27</v>
-      </c>
-      <c r="I4" t="s">
-        <v>33</v>
-      </c>
-      <c r="J4" t="s">
-        <v>34</v>
-      </c>
-      <c r="L4" t="s">
-        <v>64</v>
-      </c>
-      <c r="M4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="N12">
+        <v>22</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="2">
+        <v>1014358100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="2">
+        <v>1098665556</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="2">
+        <v>1111952949</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B5">
+      <c r="C16" s="2">
         <v>1014203666</v>
       </c>
-      <c r="E5" t="s">
-        <v>50</v>
-      </c>
-      <c r="F5" t="s">
-        <v>51</v>
-      </c>
-      <c r="H5" t="s">
-        <v>39</v>
-      </c>
-      <c r="I5" t="s">
-        <v>35</v>
-      </c>
-      <c r="J5" t="s">
-        <v>36</v>
-      </c>
-      <c r="L5" t="s">
-        <v>66</v>
-      </c>
-      <c r="M5" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" s="2">
+        <v>1017783396</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="2">
+        <v>1091159153</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19" s="2">
+        <v>1000140290</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C20" s="2">
+        <v>1006449785</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21" s="2">
+        <v>1099255828</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B6">
+      <c r="C22" s="2">
         <v>1070914841</v>
       </c>
-      <c r="E6" t="s">
-        <v>55</v>
-      </c>
-      <c r="F6" t="s">
-        <v>54</v>
-      </c>
-      <c r="H6" t="s">
-        <v>40</v>
-      </c>
-      <c r="I6" t="s">
-        <v>37</v>
-      </c>
-      <c r="L6" t="s">
-        <v>68</v>
-      </c>
-      <c r="M6" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>1006449785</v>
-      </c>
-      <c r="E7" t="s">
-        <v>52</v>
-      </c>
-      <c r="F7" t="s">
-        <v>53</v>
-      </c>
-      <c r="I7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8">
-        <v>1050119377</v>
-      </c>
-      <c r="E8" t="s">
-        <v>56</v>
-      </c>
-      <c r="F8" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9">
-        <v>1000479653</v>
-      </c>
-      <c r="E9" t="s">
-        <v>58</v>
-      </c>
-      <c r="F9" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10">
-        <v>1027805566</v>
-      </c>
-      <c r="E10" t="s">
-        <v>42</v>
-      </c>
-      <c r="F10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11">
-        <v>1098512220</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12">
-        <v>1000385262</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>12</v>
-      </c>
-      <c r="B13">
-        <v>1022843722</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14">
-        <v>1098665556</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15">
-        <v>1099255828</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16">
-        <v>1006440573</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>16</v>
-      </c>
-      <c r="B17">
-        <v>1010755944</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>17</v>
-      </c>
-      <c r="B18">
-        <v>1017783396</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>18</v>
-      </c>
-      <c r="B19">
-        <v>1014358100</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>19</v>
-      </c>
-      <c r="B20">
-        <v>1091159153</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>20</v>
-      </c>
-      <c r="B21">
-        <v>1026785300</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>21</v>
-      </c>
-      <c r="B22">
-        <v>1111952949</v>
-      </c>
+    </row>
+    <row r="23" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C23" s="2">
+        <v>1010021742</v>
+      </c>
+      <c r="D23"/>
+      <c r="E23"/>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:C22">
+    <sortCondition ref="B1:B22"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
